--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/122.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/122.xlsx
@@ -426,13 +426,13 @@
         <v>-22.20369234969773</v>
       </c>
       <c r="E2">
-        <v>-20.90244245916765</v>
+        <v>-21.96563548584448</v>
       </c>
       <c r="F2">
-        <v>-1.048511985912802</v>
+        <v>-1.896096684089853</v>
       </c>
       <c r="G2">
-        <v>-18.86084729344097</v>
+        <v>-18.28860079725944</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.31575532544312</v>
       </c>
       <c r="E3">
-        <v>-20.55149194900831</v>
+        <v>-21.95999542486537</v>
       </c>
       <c r="F3">
-        <v>-2.25041261655448</v>
+        <v>-1.799470940022902</v>
       </c>
       <c r="G3">
-        <v>-19.80329084578089</v>
+        <v>-18.34286251284114</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.19792926525372</v>
       </c>
       <c r="E4">
-        <v>-21.87288597053841</v>
+        <v>-22.09543164616802</v>
       </c>
       <c r="F4">
-        <v>-0.9868342342025588</v>
+        <v>-1.632013984444773</v>
       </c>
       <c r="G4">
-        <v>-18.36456563262707</v>
+        <v>-17.62139107732076</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.83853719859634</v>
       </c>
       <c r="E5">
-        <v>-22.83562112169029</v>
+        <v>-22.25497310599999</v>
       </c>
       <c r="F5">
-        <v>-0.7340206447051637</v>
+        <v>-1.872411174941607</v>
       </c>
       <c r="G5">
-        <v>-16.91805387373025</v>
+        <v>-17.24722177326699</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.24040370547985</v>
       </c>
       <c r="E6">
-        <v>-22.04601673782522</v>
+        <v>-23.49870207575579</v>
       </c>
       <c r="F6">
-        <v>-0.6479474729824755</v>
+        <v>-1.295978463825126</v>
       </c>
       <c r="G6">
-        <v>-17.13253698486857</v>
+        <v>-17.56825850877471</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.42892120041045</v>
       </c>
       <c r="E7">
-        <v>-23.49608555262115</v>
+        <v>-24.38035408221305</v>
       </c>
       <c r="F7">
-        <v>-0.8291445586708392</v>
+        <v>-1.515727768439779</v>
       </c>
       <c r="G7">
-        <v>-17.03087459049062</v>
+        <v>-16.85390918449889</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-19.43155121000772</v>
       </c>
       <c r="E8">
-        <v>-23.36967841273867</v>
+        <v>-24.39223226660205</v>
       </c>
       <c r="F8">
-        <v>-0.7312663230908553</v>
+        <v>-1.211155298513262</v>
       </c>
       <c r="G8">
-        <v>-16.72116587576373</v>
+        <v>-16.38589536074526</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.27297136083996</v>
       </c>
       <c r="E9">
-        <v>-22.53042654069659</v>
+        <v>-25.27509701076616</v>
       </c>
       <c r="F9">
-        <v>-1.248026759979271</v>
+        <v>-1.150615723614466</v>
       </c>
       <c r="G9">
-        <v>-17.04459013720003</v>
+        <v>-16.1511828951427</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.00538448735727</v>
       </c>
       <c r="E10">
-        <v>-23.3029736856506</v>
+        <v>-25.69647352536061</v>
       </c>
       <c r="F10">
-        <v>-0.4633267448183412</v>
+        <v>-1.462476998318215</v>
       </c>
       <c r="G10">
-        <v>-16.10587603350852</v>
+        <v>-15.39416095052513</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.66542153824826</v>
       </c>
       <c r="E11">
-        <v>-24.07589877283516</v>
+        <v>-26.19139510609513</v>
       </c>
       <c r="F11">
-        <v>-0.5913848899845197</v>
+        <v>-1.322550005004726</v>
       </c>
       <c r="G11">
-        <v>-15.5290150462622</v>
+        <v>-15.04620221679384</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.34021799709222</v>
       </c>
       <c r="E12">
-        <v>-25.73117775919088</v>
+        <v>-26.50781166408852</v>
       </c>
       <c r="F12">
-        <v>-0.4740383637039416</v>
+        <v>-1.242359898576719</v>
       </c>
       <c r="G12">
-        <v>-14.68990215409395</v>
+        <v>-14.51133897241247</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.07417213515552</v>
       </c>
       <c r="E13">
-        <v>-26.62644399237092</v>
+        <v>-27.384467357322</v>
       </c>
       <c r="F13">
-        <v>-0.5113985619376021</v>
+        <v>-1.237570278253733</v>
       </c>
       <c r="G13">
-        <v>-14.69828264423143</v>
+        <v>-13.97212492217</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.9431116465884</v>
       </c>
       <c r="E14">
-        <v>-27.13949849374964</v>
+        <v>-28.26545692657294</v>
       </c>
       <c r="F14">
-        <v>-0.1718573904693072</v>
+        <v>-0.7296211854288955</v>
       </c>
       <c r="G14">
-        <v>-12.41958821468348</v>
+        <v>-13.33798680933924</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.96972295069637</v>
       </c>
       <c r="E15">
-        <v>-26.86944838698664</v>
+        <v>-29.50047868878625</v>
       </c>
       <c r="F15">
-        <v>-0.227164168484619</v>
+        <v>-0.7093162436514741</v>
       </c>
       <c r="G15">
-        <v>-12.12406106457552</v>
+        <v>-12.89850972933877</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.17724093723239</v>
       </c>
       <c r="E16">
-        <v>-29.12781726642637</v>
+        <v>-29.51832088463771</v>
       </c>
       <c r="F16">
-        <v>0.3112224561886833</v>
+        <v>-0.5909392283218134</v>
       </c>
       <c r="G16">
-        <v>-12.41374928440545</v>
+        <v>-12.49554130170044</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.563688708768799</v>
       </c>
       <c r="E17">
-        <v>-30.18893576404645</v>
+        <v>-30.11782032653141</v>
       </c>
       <c r="F17">
-        <v>-0.3846649762485002</v>
+        <v>-0.5082607062157977</v>
       </c>
       <c r="G17">
-        <v>-12.2753041094833</v>
+        <v>-12.40551107984819</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.110319144803478</v>
       </c>
       <c r="E18">
-        <v>-30.80492345489972</v>
+        <v>-31.12469580764357</v>
       </c>
       <c r="F18">
-        <v>0.6263474984594628</v>
+        <v>-0.2850065791199001</v>
       </c>
       <c r="G18">
-        <v>-11.27819287077777</v>
+        <v>-11.83894034240774</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.799919500247389</v>
       </c>
       <c r="E19">
-        <v>-31.25393336104392</v>
+        <v>-31.74192530868296</v>
       </c>
       <c r="F19">
-        <v>-0.1019928837171969</v>
+        <v>-0.1853365848476607</v>
       </c>
       <c r="G19">
-        <v>-10.85869973524998</v>
+        <v>-11.29451132984452</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.585155967455613</v>
       </c>
       <c r="E20">
-        <v>-30.81885747889452</v>
+        <v>-32.37842571026956</v>
       </c>
       <c r="F20">
-        <v>0.5210777405442989</v>
+        <v>-0.1676045522233345</v>
       </c>
       <c r="G20">
-        <v>-10.70221431520324</v>
+        <v>-11.21310439737673</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.44595051180789</v>
       </c>
       <c r="E21">
-        <v>-33.63544495626481</v>
+        <v>-32.62706808925873</v>
       </c>
       <c r="F21">
-        <v>0.3496280540846768</v>
+        <v>-0.1726725039936619</v>
       </c>
       <c r="G21">
-        <v>-11.27460570770958</v>
+        <v>-11.0995069841005</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.331890813065735</v>
       </c>
       <c r="E22">
-        <v>-32.37974435486519</v>
+        <v>-33.44705944378192</v>
       </c>
       <c r="F22">
-        <v>0.4422428431872727</v>
+        <v>0.1750098623093466</v>
       </c>
       <c r="G22">
-        <v>-9.87300528264139</v>
+        <v>-10.77301901388653</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.230624194832588</v>
       </c>
       <c r="E23">
-        <v>-32.75347938235254</v>
+        <v>-33.28479555392653</v>
       </c>
       <c r="F23">
-        <v>1.028054330038249</v>
+        <v>0.4157375713998969</v>
       </c>
       <c r="G23">
-        <v>-10.67379374958439</v>
+        <v>-11.0518569791958</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.113389774164265</v>
       </c>
       <c r="E24">
-        <v>-34.47418598331394</v>
+        <v>-33.820599270337</v>
       </c>
       <c r="F24">
-        <v>0.7254003590166165</v>
+        <v>0.3018726733132853</v>
       </c>
       <c r="G24">
-        <v>-9.864139194009969</v>
+        <v>-10.47304446036762</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.977230318476766</v>
       </c>
       <c r="E25">
-        <v>-35.36963288118661</v>
+        <v>-34.28775040354805</v>
       </c>
       <c r="F25">
-        <v>-0.3034800005697318</v>
+        <v>0.1459474203495287</v>
       </c>
       <c r="G25">
-        <v>-9.916163501477083</v>
+        <v>-10.59503933362116</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.821511860865766</v>
       </c>
       <c r="E26">
-        <v>-33.65071631430621</v>
+        <v>-34.4334139077381</v>
       </c>
       <c r="F26">
-        <v>0.3553727820230914</v>
+        <v>0.1560385920504323</v>
       </c>
       <c r="G26">
-        <v>-11.01181990551878</v>
+        <v>-10.6462334243083</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.655065342782284</v>
       </c>
       <c r="E27">
-        <v>-34.15090416700061</v>
+        <v>-34.432319536554</v>
       </c>
       <c r="F27">
-        <v>0.5137831371952464</v>
+        <v>-0.01249441278393269</v>
       </c>
       <c r="G27">
-        <v>-9.488877293344823</v>
+        <v>-10.50257198169311</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.501565052372943</v>
       </c>
       <c r="E28">
-        <v>-34.06458382282537</v>
+        <v>-33.77922082590773</v>
       </c>
       <c r="F28">
-        <v>0.522308694504859</v>
+        <v>0.2103148810166615</v>
       </c>
       <c r="G28">
-        <v>-9.651751205406017</v>
+        <v>-10.62571688793903</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.373803674340851</v>
       </c>
       <c r="E29">
-        <v>-32.87740497846843</v>
+        <v>-33.99503829919112</v>
       </c>
       <c r="F29">
-        <v>0.4907023362510438</v>
+        <v>0.1825181844483213</v>
       </c>
       <c r="G29">
-        <v>-10.16082682008867</v>
+        <v>-10.61730767961106</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.304503167655808</v>
       </c>
       <c r="E30">
-        <v>-32.98953337781615</v>
+        <v>-33.84154183844245</v>
       </c>
       <c r="F30">
-        <v>0.7815586987220062</v>
+        <v>0.1987409316647468</v>
       </c>
       <c r="G30">
-        <v>-10.76018459347662</v>
+        <v>-10.42549627450197</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.298616538018337</v>
       </c>
       <c r="E31">
-        <v>-33.7976922332749</v>
+        <v>-33.33403602739369</v>
       </c>
       <c r="F31">
-        <v>-0.2608306764691965</v>
+        <v>0.3474411641412861</v>
       </c>
       <c r="G31">
-        <v>-10.67542415958154</v>
+        <v>-10.75031075743303</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.379783240701288</v>
       </c>
       <c r="E32">
-        <v>-32.66574486972119</v>
+        <v>-33.7752171301906</v>
       </c>
       <c r="F32">
-        <v>0.05077297597228234</v>
+        <v>0.1479156212985804</v>
       </c>
       <c r="G32">
-        <v>-10.62189997934683</v>
+        <v>-10.43908128398182</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.541951923619052</v>
       </c>
       <c r="E33">
-        <v>-32.83490932019279</v>
+        <v>-33.65702711891429</v>
       </c>
       <c r="F33">
-        <v>0.3983435126759129</v>
+        <v>0.1268601786542225</v>
       </c>
       <c r="G33">
-        <v>-10.86534799635125</v>
+        <v>-11.15676191835591</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.783400633367543</v>
       </c>
       <c r="E34">
-        <v>-31.888247096868</v>
+        <v>-32.87724092662111</v>
       </c>
       <c r="F34">
-        <v>-0.4810065902962911</v>
+        <v>0.2166402945044386</v>
       </c>
       <c r="G34">
-        <v>-10.20639084006508</v>
+        <v>-10.51706814103526</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.084275938810705</v>
       </c>
       <c r="E35">
-        <v>-33.08483088827001</v>
+        <v>-32.99641732558706</v>
       </c>
       <c r="F35">
-        <v>0.923782754843459</v>
+        <v>0.06690791624401111</v>
       </c>
       <c r="G35">
-        <v>-9.276273918312103</v>
+        <v>-10.88449389181018</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.419507086364009</v>
       </c>
       <c r="E36">
-        <v>-31.80707050491856</v>
+        <v>-32.34267902039676</v>
       </c>
       <c r="F36">
-        <v>0.3662003723450837</v>
+        <v>0.007174342828138766</v>
       </c>
       <c r="G36">
-        <v>-10.36038952588878</v>
+        <v>-11.06603984918702</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.768206038782884</v>
       </c>
       <c r="E37">
-        <v>-32.35808535780621</v>
+        <v>-32.48226429981292</v>
       </c>
       <c r="F37">
-        <v>0.594884447766332</v>
+        <v>0.2429649821980041</v>
       </c>
       <c r="G37">
-        <v>-10.93525851501209</v>
+        <v>-10.68243139806408</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.098619134746762</v>
       </c>
       <c r="E38">
-        <v>-29.61627437373379</v>
+        <v>-31.64294597638965</v>
       </c>
       <c r="F38">
-        <v>0.2526693063218002</v>
+        <v>0.1580134199387064</v>
       </c>
       <c r="G38">
-        <v>-9.75579851496795</v>
+        <v>-11.39551190046863</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.405092644834262</v>
       </c>
       <c r="E39">
-        <v>-30.74305306579375</v>
+        <v>-30.82765605708617</v>
       </c>
       <c r="F39">
-        <v>0.575565263198242</v>
+        <v>0.4133344775643756</v>
       </c>
       <c r="G39">
-        <v>-10.99972302045586</v>
+        <v>-11.18050925115668</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.666586900079478</v>
       </c>
       <c r="E40">
-        <v>-29.53341988440912</v>
+        <v>-30.46584905252373</v>
       </c>
       <c r="F40">
-        <v>0.794396736730593</v>
+        <v>0.3448931060102748</v>
       </c>
       <c r="G40">
-        <v>-12.89708034667514</v>
+        <v>-11.38556757432108</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.894689055431314</v>
       </c>
       <c r="E41">
-        <v>-30.03193814615094</v>
+        <v>-30.48177454134878</v>
       </c>
       <c r="F41">
-        <v>1.140841522133819</v>
+        <v>0.7152478881279057</v>
       </c>
       <c r="G41">
-        <v>-11.22974528340048</v>
+        <v>-11.34760212647711</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.08469691168733</v>
       </c>
       <c r="E42">
-        <v>-28.91635443521706</v>
+        <v>-29.58357198776209</v>
       </c>
       <c r="F42">
-        <v>0.5426765922048932</v>
+        <v>0.3562450528982392</v>
       </c>
       <c r="G42">
-        <v>-12.11222525397171</v>
+        <v>-11.87854011636575</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.25220966395758</v>
       </c>
       <c r="E43">
-        <v>-29.45234504613714</v>
+        <v>-28.88026718201562</v>
       </c>
       <c r="F43">
-        <v>1.13267216280741</v>
+        <v>0.573123236094789</v>
       </c>
       <c r="G43">
-        <v>-11.78470865038884</v>
+        <v>-11.27964966625961</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.40487370090001</v>
       </c>
       <c r="E44">
-        <v>-27.25603760352433</v>
+        <v>-29.35325980695505</v>
       </c>
       <c r="F44">
-        <v>0.881239461770482</v>
+        <v>0.5432108891796988</v>
       </c>
       <c r="G44">
-        <v>-11.49042290933396</v>
+        <v>-11.71489864539477</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.55263703250991</v>
       </c>
       <c r="E45">
-        <v>-28.11532456699738</v>
+        <v>-28.34908391320403</v>
       </c>
       <c r="F45">
-        <v>1.472957208203419</v>
+        <v>0.4906493207372646</v>
       </c>
       <c r="G45">
-        <v>-11.51136238632699</v>
+        <v>-11.82912524811745</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.70769253571069</v>
       </c>
       <c r="E46">
-        <v>-27.86768934175448</v>
+        <v>-27.66755854764496</v>
       </c>
       <c r="F46">
-        <v>1.193138013007357</v>
+        <v>0.7014091822967372</v>
       </c>
       <c r="G46">
-        <v>-12.562800609229</v>
+        <v>-11.84744484291329</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.86528411907817</v>
       </c>
       <c r="E47">
-        <v>-28.30139674077235</v>
+        <v>-27.40339354132924</v>
       </c>
       <c r="F47">
-        <v>1.368210150119422</v>
+        <v>1.033095774051687</v>
       </c>
       <c r="G47">
-        <v>-12.26826423669337</v>
+        <v>-12.39816313919651</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.03932843035818</v>
       </c>
       <c r="E48">
-        <v>-26.3924728323867</v>
+        <v>-27.20693003281955</v>
       </c>
       <c r="F48">
-        <v>0.9691424970859542</v>
+        <v>0.8312060706413917</v>
       </c>
       <c r="G48">
-        <v>-13.3698744437751</v>
+        <v>-12.33258906730151</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.21486943061999</v>
       </c>
       <c r="E49">
-        <v>-27.50510568667429</v>
+        <v>-26.80555123075415</v>
       </c>
       <c r="F49">
-        <v>1.687979848417698</v>
+        <v>0.6472190435403992</v>
       </c>
       <c r="G49">
-        <v>-12.43876021758832</v>
+        <v>-12.58283937933808</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.40554919664911</v>
       </c>
       <c r="E50">
-        <v>-25.85633062925326</v>
+        <v>-26.02799115973108</v>
       </c>
       <c r="F50">
-        <v>1.541277638116711</v>
+        <v>0.5985516302585254</v>
       </c>
       <c r="G50">
-        <v>-11.70729224102856</v>
+        <v>-12.72207299912675</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.59764183311296</v>
       </c>
       <c r="E51">
-        <v>-24.93035555153744</v>
+        <v>-25.83253272836199</v>
       </c>
       <c r="F51">
-        <v>1.685224698435987</v>
+        <v>0.7556291422795761</v>
       </c>
       <c r="G51">
-        <v>-12.5146193178</v>
+        <v>-12.19632125336835</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.7980856387739</v>
       </c>
       <c r="E52">
-        <v>-25.29653588762492</v>
+        <v>-25.52586791055931</v>
       </c>
       <c r="F52">
-        <v>0.9252489651464141</v>
+        <v>0.6562962935402762</v>
       </c>
       <c r="G52">
-        <v>-12.72264866830909</v>
+        <v>-12.87026669435211</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.99905312553898</v>
       </c>
       <c r="E53">
-        <v>-23.55431772860657</v>
+        <v>-24.27067607754697</v>
       </c>
       <c r="F53">
-        <v>1.161381720253636</v>
+        <v>0.8207371634048116</v>
       </c>
       <c r="G53">
-        <v>-13.76998802220305</v>
+        <v>-12.98356256662806</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.19622208702817</v>
       </c>
       <c r="E54">
-        <v>-22.80073414656173</v>
+        <v>-24.63178534260684</v>
       </c>
       <c r="F54">
-        <v>1.200858397201449</v>
+        <v>0.5834645747513381</v>
       </c>
       <c r="G54">
-        <v>-14.67000436419278</v>
+        <v>-12.74148910665086</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.38938276723816</v>
       </c>
       <c r="E55">
-        <v>-23.72079920456232</v>
+        <v>-23.88707717316316</v>
       </c>
       <c r="F55">
-        <v>0.9319189794737557</v>
+        <v>0.4811264090746815</v>
       </c>
       <c r="G55">
-        <v>-13.62428497731761</v>
+        <v>-13.3517167151439</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.56451625770542</v>
       </c>
       <c r="E56">
-        <v>-23.56445571745048</v>
+        <v>-24.11647564747874</v>
       </c>
       <c r="F56">
-        <v>0.7933761880903439</v>
+        <v>0.4993314394860062</v>
       </c>
       <c r="G56">
-        <v>-12.90700639761055</v>
+        <v>-13.44584711137649</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.73017086804713</v>
       </c>
       <c r="E57">
-        <v>-24.00640308773681</v>
+        <v>-22.91415419463148</v>
       </c>
       <c r="F57">
-        <v>0.5403563351096518</v>
+        <v>0.5481347050219391</v>
       </c>
       <c r="G57">
-        <v>-12.73763564763437</v>
+        <v>-13.68994389841181</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.8665701187455</v>
       </c>
       <c r="E58">
-        <v>-23.2969016906937</v>
+        <v>-22.84838394009149</v>
       </c>
       <c r="F58">
-        <v>0.7324563925536627</v>
+        <v>0.5313735189936939</v>
       </c>
       <c r="G58">
-        <v>-13.9021439134052</v>
+        <v>-13.23462220948788</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.98723600383421</v>
       </c>
       <c r="E59">
-        <v>-21.37158090399763</v>
+        <v>-22.60881840445273</v>
       </c>
       <c r="F59">
-        <v>1.458469062328456</v>
+        <v>0.6357279309287645</v>
       </c>
       <c r="G59">
-        <v>-14.83417059482658</v>
+        <v>-13.78282635872985</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.07643099673982</v>
       </c>
       <c r="E60">
-        <v>-22.3248301204836</v>
+        <v>-22.41083897380948</v>
       </c>
       <c r="F60">
-        <v>1.68220447088538</v>
+        <v>0.622368021456414</v>
       </c>
       <c r="G60">
-        <v>-14.69285360085421</v>
+        <v>-13.84734960592692</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.1431174594606</v>
       </c>
       <c r="E61">
-        <v>-21.66550782266707</v>
+        <v>-22.24880974039394</v>
       </c>
       <c r="F61">
-        <v>0.6330953793226676</v>
+        <v>0.3998701937992724</v>
       </c>
       <c r="G61">
-        <v>-14.19188826424384</v>
+        <v>-13.3363224596624</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.18153666247311</v>
       </c>
       <c r="E62">
-        <v>-21.58220686312499</v>
+        <v>-22.04062586952559</v>
       </c>
       <c r="F62">
-        <v>0.9859600120975898</v>
+        <v>0.3886888905962847</v>
       </c>
       <c r="G62">
-        <v>-13.66799797937891</v>
+        <v>-13.6691780359341</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.19368119472697</v>
       </c>
       <c r="E63">
-        <v>-21.78447656106679</v>
+        <v>-21.52522895695967</v>
       </c>
       <c r="F63">
-        <v>1.077713299101274</v>
+        <v>0.1831079820391146</v>
       </c>
       <c r="G63">
-        <v>-13.64996034499891</v>
+        <v>-14.11644296704985</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.18538754171719</v>
       </c>
       <c r="E64">
-        <v>-19.73123271235468</v>
+        <v>-21.92456853226458</v>
       </c>
       <c r="F64">
-        <v>0.8859180808614935</v>
+        <v>0.08292191487493115</v>
       </c>
       <c r="G64">
-        <v>-14.51535951908278</v>
+        <v>-13.59628604695021</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.15011727906188</v>
       </c>
       <c r="E65">
-        <v>-19.4612864358748</v>
+        <v>-21.32665146388564</v>
       </c>
       <c r="F65">
-        <v>1.196060493204434</v>
+        <v>0.2808172306689274</v>
       </c>
       <c r="G65">
-        <v>-14.7299588083554</v>
+        <v>-13.87492037418137</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.10306551712945</v>
       </c>
       <c r="E66">
-        <v>-21.0774712440299</v>
+        <v>-20.87692097557658</v>
       </c>
       <c r="F66">
-        <v>0.3458564972997306</v>
+        <v>0.1237811370180168</v>
       </c>
       <c r="G66">
-        <v>-13.76347029833133</v>
+        <v>-14.05155291023773</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.03037040875285</v>
       </c>
       <c r="E67">
-        <v>-20.79306348571696</v>
+        <v>-20.90443600060357</v>
       </c>
       <c r="F67">
-        <v>0.8819982463114463</v>
+        <v>0.01705179573912007</v>
       </c>
       <c r="G67">
-        <v>-15.37105977701066</v>
+        <v>-13.99234644440046</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.95292851962928</v>
       </c>
       <c r="E68">
-        <v>-19.0719353338061</v>
+        <v>-21.06621188812829</v>
       </c>
       <c r="F68">
-        <v>0.6356682884757628</v>
+        <v>-0.11092102758457</v>
       </c>
       <c r="G68">
-        <v>-13.81721508648399</v>
+        <v>-13.8773509773957</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.86031421005757</v>
       </c>
       <c r="E69">
-        <v>-18.64295013606455</v>
+        <v>-20.83480741274282</v>
       </c>
       <c r="F69">
-        <v>0.8341732826782196</v>
+        <v>0.1553469052690947</v>
       </c>
       <c r="G69">
-        <v>-14.26206246810838</v>
+        <v>-13.77520951138528</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.76957238938377</v>
       </c>
       <c r="E70">
-        <v>-20.09796957875968</v>
+        <v>-21.01849149000601</v>
       </c>
       <c r="F70">
-        <v>0.1934923958006092</v>
+        <v>0.01893715994789175</v>
       </c>
       <c r="G70">
-        <v>-13.50640463753966</v>
+        <v>-13.97975351786523</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.67974609042666</v>
       </c>
       <c r="E71">
-        <v>-19.31457424582523</v>
+        <v>-21.26502196103651</v>
       </c>
       <c r="F71">
-        <v>0.6348018161724346</v>
+        <v>0.06589896474740131</v>
       </c>
       <c r="G71">
-        <v>-14.2347932408542</v>
+        <v>-13.53426650381602</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.59802114752357</v>
       </c>
       <c r="E72">
-        <v>-19.467694840949</v>
+        <v>-21.00643471753003</v>
       </c>
       <c r="F72">
-        <v>0.7416678380727932</v>
+        <v>-0.3304582701441061</v>
       </c>
       <c r="G72">
-        <v>-14.14993620940924</v>
+        <v>-13.44809104635256</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.53191209481662</v>
       </c>
       <c r="E73">
-        <v>-18.76493825909742</v>
+        <v>-21.6423453631085</v>
       </c>
       <c r="F73">
-        <v>0.2863747475743093</v>
+        <v>-0.07333219994773679</v>
       </c>
       <c r="G73">
-        <v>-13.89402188698225</v>
+        <v>-13.17669239775567</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.47594817591612</v>
       </c>
       <c r="E74">
-        <v>-19.60468021007583</v>
+        <v>-21.63922214819223</v>
       </c>
       <c r="F74">
-        <v>0.4839196639569214</v>
+        <v>-0.4072222489941335</v>
       </c>
       <c r="G74">
-        <v>-13.18013466449905</v>
+        <v>-13.60107676327491</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.4428707282618</v>
       </c>
       <c r="E75">
-        <v>-22.18781567887751</v>
+        <v>-21.49971162657992</v>
       </c>
       <c r="F75">
-        <v>0.5964111288896915</v>
+        <v>-0.1503339202423676</v>
       </c>
       <c r="G75">
-        <v>-12.96009719424314</v>
+        <v>-13.38079518839972</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.4134544782601</v>
       </c>
       <c r="E76">
-        <v>-20.31310177217448</v>
+        <v>-21.84664598138815</v>
       </c>
       <c r="F76">
-        <v>-0.03796753878742029</v>
+        <v>-0.2740961520576278</v>
       </c>
       <c r="G76">
-        <v>-14.28181014019556</v>
+        <v>-12.83324372530553</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.39920950588126</v>
       </c>
       <c r="E77">
-        <v>-20.1292017279224</v>
+        <v>-21.59188384551184</v>
       </c>
       <c r="F77">
-        <v>0.5345859277817504</v>
+        <v>-0.4056392388873837</v>
       </c>
       <c r="G77">
-        <v>-13.35171932588849</v>
+        <v>-13.30708342561423</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.37788708987203</v>
       </c>
       <c r="E78">
-        <v>-23.10106531709406</v>
+        <v>-22.60649675932215</v>
       </c>
       <c r="F78">
-        <v>0.6445293345835091</v>
+        <v>-0.4501002024978416</v>
       </c>
       <c r="G78">
-        <v>-14.48530201660529</v>
+        <v>-12.86969755203125</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.35484144598564</v>
       </c>
       <c r="E79">
-        <v>-21.83666996778591</v>
+        <v>-22.31830127228097</v>
       </c>
       <c r="F79">
-        <v>0.1484292090883161</v>
+        <v>-0.4987874965973825</v>
       </c>
       <c r="G79">
-        <v>-12.91177753335081</v>
+        <v>-12.23110811967264</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.31680280397905</v>
       </c>
       <c r="E80">
-        <v>-22.11439520907719</v>
+        <v>-23.35007525528548</v>
       </c>
       <c r="F80">
-        <v>0.1389526860002897</v>
+        <v>-0.6232629527464529</v>
       </c>
       <c r="G80">
-        <v>-13.05399001271794</v>
+        <v>-12.32790539150506</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.2617937709439</v>
       </c>
       <c r="E81">
-        <v>-23.67079454021139</v>
+        <v>-23.78281495606466</v>
       </c>
       <c r="F81">
-        <v>0.5680536275896561</v>
+        <v>-0.5428359332412461</v>
       </c>
       <c r="G81">
-        <v>-11.51302151451464</v>
+        <v>-11.96231891029458</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.18888323757888</v>
       </c>
       <c r="E82">
-        <v>-23.33151040066349</v>
+        <v>-24.30372733326996</v>
       </c>
       <c r="F82">
-        <v>0.2160355863003949</v>
+        <v>-0.6330898752458635</v>
       </c>
       <c r="G82">
-        <v>-12.74623021882832</v>
+        <v>-12.35655178653105</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.08945903383514</v>
       </c>
       <c r="E83">
-        <v>-22.46739740563099</v>
+        <v>-25.36454887628031</v>
       </c>
       <c r="F83">
-        <v>-0.3077701153488305</v>
+        <v>-0.8022292450190778</v>
       </c>
       <c r="G83">
-        <v>-13.37720410921465</v>
+        <v>-11.93603523912354</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.97459245718785</v>
       </c>
       <c r="E84">
-        <v>-25.07095421451686</v>
+        <v>-25.76539606729614</v>
       </c>
       <c r="F84">
-        <v>0.6769035894197195</v>
+        <v>-0.7999603467028099</v>
       </c>
       <c r="G84">
-        <v>-12.75225581734461</v>
+        <v>-11.69398266510306</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.83169081374456</v>
       </c>
       <c r="E85">
-        <v>-26.18962583807075</v>
+        <v>-26.6365778280035</v>
       </c>
       <c r="F85">
-        <v>0.582919509000296</v>
+        <v>-0.5270555342179156</v>
       </c>
       <c r="G85">
-        <v>-13.18131472105424</v>
+        <v>-11.23121252186069</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.68216413219209</v>
       </c>
       <c r="E86">
-        <v>-27.18549530917211</v>
+        <v>-27.62003750366627</v>
       </c>
       <c r="F86">
-        <v>0.05857039833483409</v>
+        <v>-0.622234120432176</v>
       </c>
       <c r="G86">
-        <v>-11.83499420195828</v>
+        <v>-11.50629884719252</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.51758675188879</v>
       </c>
       <c r="E87">
-        <v>-25.82116123575461</v>
+        <v>-28.28776174799293</v>
       </c>
       <c r="F87">
-        <v>-0.664735995135013</v>
+        <v>-0.5639518467060084</v>
       </c>
       <c r="G87">
-        <v>-10.96120148401398</v>
+        <v>-11.38532216432951</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.35939243935427</v>
       </c>
       <c r="E88">
-        <v>-30.50259874293147</v>
+        <v>-29.13282603928411</v>
       </c>
       <c r="F88">
-        <v>0.3780244886526438</v>
+        <v>-0.6833469255737095</v>
       </c>
       <c r="G88">
-        <v>-11.32417983137794</v>
+        <v>-11.20850165466259</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.21067895907398</v>
       </c>
       <c r="E89">
-        <v>-29.61922107716876</v>
+        <v>-29.9218552033807</v>
       </c>
       <c r="F89">
-        <v>0.9457527151005074</v>
+        <v>-0.7129337240994995</v>
       </c>
       <c r="G89">
-        <v>-10.78215270383854</v>
+        <v>-10.84292953254736</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.08707903193057</v>
       </c>
       <c r="E90">
-        <v>-30.9851603667633</v>
+        <v>-31.42023832551837</v>
       </c>
       <c r="F90">
-        <v>-0.1005954279086741</v>
+        <v>-0.9320385588747743</v>
       </c>
       <c r="G90">
-        <v>-10.53605086495725</v>
+        <v>-11.18992751226912</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.00167907978109</v>
       </c>
       <c r="E91">
-        <v>-32.71045418963298</v>
+        <v>-32.62569545291588</v>
       </c>
       <c r="F91">
-        <v>0.1977336369029426</v>
+        <v>-0.9193645376119418</v>
       </c>
       <c r="G91">
-        <v>-11.00764532491759</v>
+        <v>-10.94685413711352</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.95793554222909</v>
       </c>
       <c r="E92">
-        <v>-34.30557598655421</v>
+        <v>-34.37993508211394</v>
       </c>
       <c r="F92">
-        <v>-0.4802221263658399</v>
+        <v>-0.8808578788928069</v>
       </c>
       <c r="G92">
-        <v>-11.68539984225978</v>
+        <v>-10.67210720857853</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.97233834715116</v>
       </c>
       <c r="E93">
-        <v>-35.26536235766547</v>
+        <v>-35.61670742290066</v>
       </c>
       <c r="F93">
-        <v>-0.05294359306263256</v>
+        <v>-0.8988259962269309</v>
       </c>
       <c r="G93">
-        <v>-10.83826282659075</v>
+        <v>-10.79747646921608</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.03052904763882</v>
       </c>
       <c r="E94">
-        <v>-37.32678387947616</v>
+        <v>-37.58943088705266</v>
       </c>
       <c r="F94">
-        <v>0.4461154607953604</v>
+        <v>-0.999802325893385</v>
       </c>
       <c r="G94">
-        <v>-11.0029120449739</v>
+        <v>-11.05662419881917</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.14359077676581</v>
       </c>
       <c r="E95">
-        <v>-38.59617138879675</v>
+        <v>-39.29365546887148</v>
       </c>
       <c r="F95">
-        <v>0.1367931321811914</v>
+        <v>-1.548474788607249</v>
       </c>
       <c r="G95">
-        <v>-11.5681447758114</v>
+        <v>-11.3453125034707</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.28352160721565</v>
       </c>
       <c r="E96">
-        <v>-42.14853763126235</v>
+        <v>-41.0548475738273</v>
       </c>
       <c r="F96">
-        <v>-0.4376548106381817</v>
+        <v>-1.212038338164646</v>
       </c>
       <c r="G96">
-        <v>-10.44230033206267</v>
+        <v>-11.27040501966248</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.44579303130368</v>
       </c>
       <c r="E97">
-        <v>-43.27936362775836</v>
+        <v>-42.37886434830903</v>
       </c>
       <c r="F97">
-        <v>-0.433191567071898</v>
+        <v>-1.214410782406264</v>
       </c>
       <c r="G97">
-        <v>-11.89983857074005</v>
+        <v>-11.4367969100602</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.60172979278859</v>
       </c>
       <c r="E98">
-        <v>-45.78209292531136</v>
+        <v>-45.23840433720071</v>
       </c>
       <c r="F98">
-        <v>-0.7044205923009289</v>
+        <v>-1.340095654963422</v>
       </c>
       <c r="G98">
-        <v>-11.71335961145831</v>
+        <v>-11.71251373021079</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.73406008678739</v>
       </c>
       <c r="E99">
-        <v>-45.51529997452985</v>
+        <v>-46.34540232202334</v>
       </c>
       <c r="F99">
-        <v>-0.613264558194663</v>
+        <v>-1.641840906944184</v>
       </c>
       <c r="G99">
-        <v>-11.53833790481466</v>
+        <v>-11.59389063359667</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.82604921219729</v>
       </c>
       <c r="E100">
-        <v>-48.29785500000168</v>
+        <v>-48.81302140933907</v>
       </c>
       <c r="F100">
-        <v>-0.107165209780277</v>
+        <v>-1.760934460077266</v>
       </c>
       <c r="G100">
-        <v>-11.70645419201481</v>
+        <v>-11.80543535169769</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.85887782076829</v>
       </c>
       <c r="E101">
-        <v>-50.33915628954924</v>
+        <v>-49.52783164875814</v>
       </c>
       <c r="F101">
-        <v>-1.266908566558683</v>
+        <v>-1.575054613460876</v>
       </c>
       <c r="G101">
-        <v>-12.39556283758376</v>
+        <v>-11.72796672744559</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.83877617691614</v>
       </c>
       <c r="E102">
-        <v>-52.03957237658319</v>
+        <v>-51.92942505903741</v>
       </c>
       <c r="F102">
-        <v>-0.927842049612192</v>
+        <v>-1.906260752122203</v>
       </c>
       <c r="G102">
-        <v>-13.23790130469432</v>
+        <v>-12.43227643339629</v>
       </c>
     </row>
   </sheetData>
